--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="401">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1136,7 +1136,10 @@
     <t>Invoice.lineItem.priceComponent:va-interest-charged.amount</t>
   </si>
   <si>
-    <t>2001: source value from AR TRANSACTION - INT.CHARGE (433-25)</t>
+    <t>2001: source value from AR TRANSACTION - INT.CHARGE (433-27)</t>
+  </si>
+  <si>
+    <t>IB.ARTransaction.InterestCharge</t>
   </si>
   <si>
     <t>Invoice.lineItem.priceComponent:va-admin-charged</t>
@@ -1187,7 +1190,10 @@
     <t>Invoice.lineItem.priceComponent:va-admin-charged.amount</t>
   </si>
   <si>
-    <t>2002: source value from AR TRANSACTION - ADM.CHARGE (433-25)</t>
+    <t>2002: source value from AR TRANSACTION - ADM.CHARGE (433-28)</t>
+  </si>
+  <si>
+    <t>IB.ARTransaction.AdministrativeCharge</t>
   </si>
   <si>
     <t>Invoice.totalPriceComponent</t>
@@ -10692,7 +10698,7 @@
         <v>360</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>281</v>
@@ -10709,13 +10715,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>261</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>79</v>
@@ -10829,7 +10835,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>265</v>
@@ -10947,7 +10953,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>266</v>
@@ -11067,7 +11073,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>267</v>
@@ -11189,7 +11195,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>268</v>
@@ -11287,7 +11293,7 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>79</v>
@@ -11307,7 +11313,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>273</v>
@@ -11425,7 +11431,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>296</v>
@@ -11543,7 +11549,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>298</v>
@@ -11663,7 +11669,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>302</v>
@@ -11785,7 +11791,7 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>312</v>
@@ -11833,7 +11839,7 @@
         <v>79</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>79</v>
@@ -11887,7 +11893,7 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
@@ -11907,7 +11913,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>276</v>
@@ -12027,7 +12033,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>282</v>
@@ -12127,10 +12133,10 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>325</v>
+        <v>379</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>281</v>
@@ -12147,10 +12153,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12176,10 +12182,10 @@
         <v>82</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12230,7 +12236,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12265,10 +12271,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12294,10 +12300,10 @@
         <v>283</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>280</v>
@@ -12350,7 +12356,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12385,10 +12391,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12414,10 +12420,10 @@
         <v>283</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>280</v>
@@ -12470,7 +12476,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -12505,10 +12511,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12531,16 +12537,16 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12590,7 +12596,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -12625,10 +12631,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12651,13 +12657,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12708,7 +12714,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -12729,16 +12735,16 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
+++ b/docs/StructureDefinition-DebtPortalInterestFeesInvoice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to Invoice</t>
+    <t>This StructureDefinition contains the maps for VistA file AR TRANSACTION (433) to Invoice.</t>
   </si>
   <si>
     <t>Purpose</t>
